--- a/result/SMAD7_LUAD_Tables.xlsx
+++ b/result/SMAD7_LUAD_Tables.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -882,27 +883,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
     </row>
@@ -929,27 +930,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>-0.076</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>-0.023</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.033</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>-0.014</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.088</t>
         </is>
       </c>
     </row>
@@ -968,27 +969,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.110</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.165</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.673</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.553</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.795</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.110</t>
         </is>
       </c>
     </row>
@@ -1015,27 +1016,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>-0.016</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.074</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1055,34 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>0.181</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.774</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.181</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1091,12 +1092,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.076</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1106,22 +1107,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.069</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.055</t>
         </is>
       </c>
     </row>
@@ -1134,40 +1135,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.110</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.468</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.317</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1177,37 +1178,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.076</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>-0.063</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.062</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.065</t>
         </is>
       </c>
     </row>
@@ -1220,40 +1221,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.468</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.239</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1263,37 +1264,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-0.023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>-0.063</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.062</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>0.037</t>
         </is>
       </c>
     </row>
@@ -1306,40 +1307,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>0.673</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.504</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1349,37 +1350,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.069</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>0.062</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.005</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.055</t>
         </is>
       </c>
     </row>
@@ -1392,40 +1393,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>0.553</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.928</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1435,32 +1436,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.065</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1478,32 +1479,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.110</t>
+          <t>0.795</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.239</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.504</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.928</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1519,7 +1520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,7 +1551,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.181</t>
         </is>
       </c>
     </row>
@@ -1561,86 +1562,146 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.904</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SMAD7group_Low</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.576</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.076</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.182</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.497</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pathologic_stage_2.0</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.156</v>
+        <v>0.993</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.217</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pathologic_stage_3.0</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.956</v>
+        <v>0.999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.209</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SMAD7group_Low</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.534</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.328</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pathologic_stage_2.0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.994</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>pathologic_stage_4.0</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2.729</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.006</t>
+      <c r="B12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.010</t>
         </is>
       </c>
     </row>
@@ -2586,4 +2647,99 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SMAD7</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.902</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.009</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SMAD7</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.045</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result/SMAD7_LUAD_Tables.xlsx
+++ b/result/SMAD7_LUAD_Tables.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +906,11 @@
           <t>BRAFExpression</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EGFR_Mut_Binary</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -951,6 +956,11 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>-0.014</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.052</t>
         </is>
       </c>
     </row>
@@ -992,6 +1002,11 @@
           <t>0.795</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1037,6 +1052,11 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>-0.016</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.019</t>
         </is>
       </c>
     </row>
@@ -1078,6 +1098,11 @@
           <t>0.774</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.731</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1123,6 +1148,11 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>-0.055</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-0.028</t>
         </is>
       </c>
     </row>
@@ -1164,6 +1194,11 @@
           <t>0.317</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.614</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1209,6 +1244,11 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0.065</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.024</t>
         </is>
       </c>
     </row>
@@ -1250,6 +1290,11 @@
           <t>0.239</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.663</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1295,6 +1340,11 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0.037</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.131</t>
         </is>
       </c>
     </row>
@@ -1336,6 +1386,11 @@
           <t>0.504</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1381,6 +1436,11 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0.005</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.011</t>
         </is>
       </c>
     </row>
@@ -1422,6 +1482,11 @@
           <t>0.928</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.847</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1467,6 +1532,11 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.089</t>
         </is>
       </c>
     </row>
@@ -1508,6 +1578,107 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.106</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EGFR_Mut_Binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.052</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-0.131</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.089</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.348</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.731</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.614</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.663</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.847</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.106</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result/SMAD7_LUAD_Tables.xlsx
+++ b/result/SMAD7_LUAD_Tables.xlsx
@@ -935,32 +935,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.076</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>-0.056</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.105</t>
         </is>
       </c>
     </row>
@@ -979,32 +979,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.110</t>
+          <t>0.049</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.493</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>0.856</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>0.843</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.019</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1132,27 +1132,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.028</t>
+          <t>-0.056</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.110</t>
+          <t>0.049</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1176,27 +1176,27 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>0.218</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.076</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-0.005</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.493</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1271,28 +1271,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>0.911</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.131</t>
+          <t>-0.111</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>0.856</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1367,28 +1367,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.014</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.029</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>0.843</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1463,28 +1463,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>0.525</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>-0.056</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.067</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1559,28 +1559,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.140</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1607,27 +1607,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.028</t>
+          <t>-0.056</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.131</t>
+          <t>-0.111</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.029</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1655,27 +1655,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>0.911</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>0.525</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.140</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>

--- a/result/SMAD7_LUAD_Tables.xlsx
+++ b/result/SMAD7_LUAD_Tables.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.080</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.247</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.865</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.102</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>0.139</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.111</t>
+          <t>0.008</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.904</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.050</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>0.469</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1580,7 +1580,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.140</t>
+          <t>0.122</t>
         </is>
       </c>
     </row>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.111</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1640,42 +1640,42 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.865</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.904</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>0.469</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.140</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>

--- a/result/SMAD7_LUAD_Tables.xlsx
+++ b/result/SMAD7_LUAD_Tables.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.125</t>
         </is>
       </c>
     </row>
@@ -509,342 +509,328 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">  FEMALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.176</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FEMALE</t>
+          <t xml:space="preserve">  MALE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MALE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>105</v>
-      </c>
-      <c r="C8" t="n">
-        <v>119</v>
-      </c>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>138</v>
+      </c>
+      <c r="C9" t="n">
+        <v>124</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.450</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>124</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.450</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>15</v>
-      </c>
+          <t>pathologic_M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pathologic_M</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>163</v>
+      </c>
+      <c r="C14" t="n">
+        <v>159</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.215</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>163</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>159</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.304</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>15</v>
-      </c>
+          <t>pathologic_N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pathologic_N</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>167</v>
+      </c>
+      <c r="C17" t="n">
+        <v>149</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.147</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>167</v>
+        <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>149</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.147</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
+          <t>pathologic_T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pathologic_T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>91</v>
+      </c>
+      <c r="C22" t="n">
+        <v>73</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.221</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="C23" t="n">
-        <v>73</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.221</t>
-        </is>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>11</v>
-      </c>
-      <c r="C26" t="n">
-        <v>7</v>
-      </c>
+          <t>SmokingStatus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmokingStatus</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>87</v>
+      </c>
+      <c r="C27" t="n">
+        <v>72</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.148</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="C28" t="n">
-        <v>72</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.177</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>159</v>
-      </c>
-      <c r="C29" t="n">
         <v>174</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -908,7 +894,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
     </row>
@@ -960,7 +946,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.056</t>
         </is>
       </c>
     </row>
@@ -1004,7 +990,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.218</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1042,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.011</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1086,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.837</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1138,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.001</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1182,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.983</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1234,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.011</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.810</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1330,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-0.123</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1374,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.007</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1426,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.024</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1470,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.595</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1522,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -1580,14 +1566,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.177</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1597,37 +1583,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.056</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1645,37 +1631,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1691,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,6 +1693,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1714,15 +1710,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>ageG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.014</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.181</t>
+        <v>1.532</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.026</t>
         </is>
       </c>
     </row>
@@ -1735,144 +1737,78 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.904</t>
+      <c r="C3" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.979</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.076</t>
+        <v>1.516</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.804</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>SMAD7group_Low</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.497</t>
+        <v>1.565</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.217</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.209</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SMAD7group_Low</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.534</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.029</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>gender_MALE</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.218</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.328</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>pathologic_stage_2.0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.135</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pathologic_stage_3.0</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.994</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.010</t>
+        <v>1.23</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.285</t>
         </is>
       </c>
     </row>

--- a/result/SMAD7_LUAD_Tables.xlsx
+++ b/result/SMAD7_LUAD_Tables.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EGFRExpression</t>
+          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.080</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.247</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>0.865</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-0.102</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.139</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>0.008</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.904</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.050</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.469</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1566,14 +1566,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.122</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFRExpression</t>
+          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1583,37 +1583,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-0.102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1631,37 +1631,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>0.865</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.904</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.469</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,21 +1710,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ageG</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.532</v>
+        <v>1.014</v>
       </c>
       <c r="C2" t="n">
-        <v>1.052</v>
+        <v>0.994</v>
       </c>
       <c r="D2" t="n">
-        <v>2.233</v>
+        <v>1.034</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.181</t>
         </is>
       </c>
     </row>
@@ -1741,74 +1741,200 @@
         <v>0.993</v>
       </c>
       <c r="D3" t="n">
-        <v>1.007</v>
+        <v>1.008</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>0.904</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.516</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1.273</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.804</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.076</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SMAD7group_Low</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.565</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1.069</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.29</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.497</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ALKExpression</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.217</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BRAFExpression</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SMAD7group_Low</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.534</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>gender_MALE</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.798</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.285</t>
+      <c r="B9" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.328</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pathologic_stage_2.0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.419</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.994</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.856</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.831</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pathologic_stage_4.0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.255</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.010</t>
         </is>
       </c>
     </row>
@@ -1886,7 +2012,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMAD7expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
+          <t>SMAD7expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -2121,7 +2247,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SMAD7expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
+          <t>SMAD7expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -2356,7 +2482,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SMAD7expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
+          <t>SMAD7expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2591,7 +2717,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SMAD7expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
+          <t>SMAD7expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
